--- a/KatalonData/ABPTestData/PaymentsCC.xlsx
+++ b/KatalonData/ABPTestData/PaymentsCC.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="374">
   <si>
     <t>Result</t>
   </si>
@@ -1160,6 +1160,39 @@
   </si>
   <si>
     <t>Fri Sep 18 01:07:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 22 20:01:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 22 20:02:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 22 20:04:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 22 20:18:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 22 21:06:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 22 21:13:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 22 21:15:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 22 23:27:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 22 23:32:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 17:51:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 17:53:32 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1594,7 +1627,7 @@
         <v>36</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1619,10 +1652,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -1648,7 +1681,7 @@
         <v>36</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -1962,10 +1995,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -2212,10 +2245,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -2813,10 +2846,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/ABPTestData/PaymentsCC.xlsx
+++ b/KatalonData/ABPTestData/PaymentsCC.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476640\Documents\VPS-Katalon\KatalonData\ABPTestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{01E1744E-7427-404A-BBE3-C5F6189627A0}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5509EB6E-DB03-4EB7-9420-E8E355739F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="15" firstSheet="14" windowHeight="10300" windowWidth="19420" xWindow="-110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-110"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="VerifySuccessfulPaymentCCNoCF" r:id="rId1" sheetId="1"/>
-    <sheet name="VerifyCFVerbiageOnRPCCDCF" r:id="rId2" sheetId="4"/>
-    <sheet name="VerifyStaticTextOnRecieptCC" r:id="rId3" sheetId="5"/>
-    <sheet name="VerifySuccessfulPaymentCCSCF" r:id="rId4" sheetId="2"/>
-    <sheet name="VerifySuccessfulPaymentCCDCF" r:id="rId5" sheetId="3"/>
-    <sheet name="VerifySuccessfulPaymentSPMCCDCF" r:id="rId6" sheetId="9"/>
-    <sheet name="UiVerificationSPPaymentMethodCC" r:id="rId7" sheetId="10"/>
-    <sheet name="VerifyStaticTextOnPPCCDCF" r:id="rId8" sheetId="6"/>
-    <sheet name="UIVerifySelectPaymentMethodCC" r:id="rId9" sheetId="7"/>
-    <sheet name="CreateVerifyDeleteCCPM" r:id="rId10" sheetId="8"/>
-    <sheet name="CreateSPDCFCC_IPDeferred" r:id="rId11" sheetId="11"/>
-    <sheet name="CreateSPDCFCC_IPDailyNOP" r:id="rId12" sheetId="12"/>
-    <sheet name="CreateSPDCFCC_IPDailyIA" r:id="rId13" sheetId="13"/>
-    <sheet name="CreateSPDCFCC_RecDaily" r:id="rId14" sheetId="14"/>
-    <sheet name="CreateSPDCFCC_RecDeferred" r:id="rId15" sheetId="15"/>
-    <sheet name="CreateSPDCFCC_AutomaticPayment" r:id="rId16" sheetId="16"/>
+    <sheet name="VerifySuccessfulPaymentCCNoCF" sheetId="1" r:id="rId1"/>
+    <sheet name="VerifyCFVerbiageOnRPCCDCF" sheetId="4" r:id="rId2"/>
+    <sheet name="VerifyStaticTextOnRecieptCC" sheetId="5" r:id="rId3"/>
+    <sheet name="VerifySuccessfulPaymentCCSCF" sheetId="2" r:id="rId4"/>
+    <sheet name="VerifySuccessfulPaymentCCDCF" sheetId="3" r:id="rId5"/>
+    <sheet name="VerifySuccessfulPaymentSPMCCDCF" sheetId="9" r:id="rId6"/>
+    <sheet name="UiVerificationSPPaymentMethodCC" sheetId="10" r:id="rId7"/>
+    <sheet name="VerifyStaticTextOnPPCCDCF" sheetId="6" r:id="rId8"/>
+    <sheet name="UIVerifySelectPaymentMethodCC" sheetId="7" r:id="rId9"/>
+    <sheet name="CreateVerifyDeleteCCPM" sheetId="8" r:id="rId10"/>
+    <sheet name="CreateSPDCFCC_IPDeferred" sheetId="11" r:id="rId11"/>
+    <sheet name="CreateSPDCFCC_IPDailyNOP" sheetId="12" r:id="rId12"/>
+    <sheet name="CreateSPDCFCC_IPDailyIA" sheetId="13" r:id="rId13"/>
+    <sheet name="CreateSPDCFCC_RecDaily" sheetId="14" r:id="rId14"/>
+    <sheet name="CreateSPDCFCC_RecDeferred" sheetId="15" r:id="rId15"/>
+    <sheet name="CreateSPDCFCC_AutomaticPayment" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="70">
   <si>
     <t>Result</t>
   </si>
@@ -95,15 +95,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>Thu May 15 17:04:09 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu May 15 17:04:32 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu May 15 17:04:51 IST 2025</t>
-  </si>
-  <si>
     <t>Mon May 19 19:55:54 IST 2025</t>
   </si>
   <si>
@@ -117,9 +108,6 @@
   </si>
   <si>
     <t>N</t>
-  </si>
-  <si>
-    <t>Tue May 20 17:19:13 IST 2025</t>
   </si>
   <si>
     <t>VTList</t>
@@ -127,9 +115,6 @@
   <si>
     <t>Payment Receipt,180RemittanceID:,Due Date,Payment Entry Date,Amount Due,Amount to Pay,UDF1:,UDF2:,UDF3:,UDF4:,Fees,Total Processed:,Total Unpaid:,
 Payment Method,Name Appearing on Card:,Card Type:,Card Number:,Billing Address:,Country:,Expiration Date:</t>
-  </si>
-  <si>
-    <t>Thu May 29 17:02:43 IST 2025</t>
   </si>
   <si>
     <t>Payment Preview,Bills Label,Due Date,Pay Date,Amount Due,Amount to Pay,Fees,Total:,Credit Card Information,
@@ -175,34 +160,10 @@
     <t>Fail</t>
   </si>
   <si>
-    <t>Wed Jun 11 14:47:43 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 11 14:48:07 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 11 14:48:26 IST 2025</t>
-  </si>
-  <si>
     <t>Visa,47****0011,Expires, 12/2028,Billing Address:,
 1853 Mandan Terace,
 CATAWBA,  North Carolina ,  20770
 United States</t>
-  </si>
-  <si>
-    <t>Wed Jun 18 15:46:11 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 18 15:51:29 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 18 15:54:24 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jun 18 16:38:57 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Jun 27 20:42:43 IST 2025</t>
   </si>
   <si>
     <t>Name Appearing on Card:,Imtiaz Ahmed,
@@ -214,9 +175,6 @@
 Country:,	UNITED STATES,</t>
   </si>
   <si>
-    <t>Thu Jul 24 20:45:30 IST 2025</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -253,852 +211,15 @@
     <t>DivideYourPaymentPlan</t>
   </si>
   <si>
-    <t>Thu Aug 28 18:45:19 IST 2025</t>
-  </si>
-  <si>
     <t>Mon Sep 08 19:16:24 IST 2025</t>
   </si>
   <si>
-    <t>Mon Sep 08 20:01:38 IST 2025</t>
-  </si>
-  <si>
     <t>IndividualAmount</t>
   </si>
   <si>
     <t>NumberOfPayments</t>
   </si>
   <si>
-    <t>Mon Sep 08 20:38:05 IST 2025</t>
-  </si>
-  <si>
-    <t>Mon Sep 08 23:14:30 IST 2025</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Fri Sep 19 20:30:11 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Sep 19 20:46:55 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Sep 19 20:50:51 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Sep 19 21:02:38 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Sep 19 21:03:38 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Sep 19 21:04:42 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Sep 19 21:05:48 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Sep 19 21:08:34 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Sep 19 21:11:20 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Sep 19 21:14:02 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Sep 19 21:16:45 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Sep 19 21:19:26 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Sep 19 21:41:27 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Sep 19 21:51:33 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Sep 19 23:05:06 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 24 16:28:11 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 24 16:32:33 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 24 16:35:22 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 24 16:37:34 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 24 16:39:45 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 24 16:40:14 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 24 16:40:46 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 24 16:41:14 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 24 16:43:45 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 24 16:46:26 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 24 16:49:10 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 24 16:51:54 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 24 16:54:39 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 24 17:15:15 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 24 17:26:03 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 25 13:09:57 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 25 13:14:04 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 25 13:16:53 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 25 13:19:03 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 25 13:21:16 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 25 13:21:46 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 25 13:22:16 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 25 13:22:50 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 25 13:25:33 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 25 13:28:15 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 25 13:30:46 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 25 13:33:20 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 25 13:36:16 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 25 13:56:22 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 25 14:06:16 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 30 18:23:15 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 30 18:23:57 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 30 18:24:34 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Oct 08 21:15:40 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 16:36:59 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 16:40:41 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 16:43:24 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 16:45:43 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 16:48:06 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 16:48:35 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 16:49:05 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 16:49:34 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 16:52:14 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 16:54:54 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 16:57:34 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 17:00:19 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 17:03:01 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 17:22:56 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 14 17:32:15 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Oct 15 00:42:59 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Oct 15 19:33:04 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Oct 15 19:36:56 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Oct 15 19:39:06 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Oct 15 19:41:23 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Oct 15 19:43:48 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Oct 15 19:44:17 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Oct 15 19:44:46 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Oct 15 19:45:21 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Oct 15 19:48:03 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Oct 15 19:50:37 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Oct 15 19:53:23 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Oct 15 19:56:17 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Oct 15 19:59:00 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Oct 17 16:48:38 IST 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 25 16:55:09 IST 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 25 18:52:46 IST 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 25 18:54:16 IST 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 25 22:33:33 IST 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 25 23:01:05 IST 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 25 23:24:17 IST 2025</t>
-  </si>
-  <si>
-    <t>Sun Oct 26 00:21:26 IST 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 27 20:51:00 IST 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 27 22:40:15 IST 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 27 23:40:16 IST 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 27 23:47:37 IST 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 27 23:54:37 IST 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 27 23:55:16 IST 2025</t>
-  </si>
-  <si>
-    <t>Mon Oct 27 23:56:33 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Oct 28 00:25:13 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 09:32:21 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 09:36:21 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 09:38:46 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 09:40:46 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 09:42:44 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 09:43:14 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 09:43:40 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 09:44:10 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 09:51:52 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 09:59:30 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 10:07:10 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 10:09:46 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 10:12:28 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 10:49:47 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 10:57:57 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 21:18:39 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Oct 31 15:02:51 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Oct 31 15:05:37 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Oct 31 15:08:30 IST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 03 21:43:50 IST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 03 22:50:54 IST 2025</t>
-  </si>
-  <si>
-    <t>Mon Dec 15 21:38:33 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 19 20:06:24 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 19 22:27:23 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Dec 25 17:39:56 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 19:16:02 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 19:21:31 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 19:24:10 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 19:26:33 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 19:29:19 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 19:29:51 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 19:30:30 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 19:31:13 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 19:33:49 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 19:36:25 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 19:39:05 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 19:41:44 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 19:44:29 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 20:05:01 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 20:14:36 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 20:23:49 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 20:24:37 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 20:25:32 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 20:26:20 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 20:27:10 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 20:27:57 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Jan 09 16:59:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 09 17:00:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 00:56:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 01:02:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 01:05:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 01:08:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 01:10:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 01:11:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 01:12:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 01:12:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 01:20:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 01:28:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 01:36:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 01:38:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 01:41:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 02:19:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 02:28:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 02:37:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 02:38:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 02:39:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 02:39:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 02:40:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 02:41:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 10 21:23:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 10:05:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 10:11:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 10:13:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 10:16:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 10:18:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 10:19:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 10:20:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 10:20:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 10:23:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 10:26:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 10:28:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 10:31:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 10:34:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 10:54:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 11:03:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 11:11:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 11:12:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 11:12:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 11:13:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 11:14:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 11:15:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jun 02 17:24:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 13:29:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 18:08:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 05 18:14:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 23:17:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 23:22:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 00:37:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 00:42:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 00:45:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 00:48:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 00:51:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 00:51:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 00:52:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 00:53:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 00:56:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 00:59:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 01:01:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 01:04:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 01:07:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 01:30:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 01:39:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 01:54:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 01:55:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 01:56:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 01:57:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 01:58:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jun 19 01:58:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 18:47:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 18:54:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 19:02:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 19:09:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 06 23:56:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 10:34:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 10:39:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 10:42:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 10:44:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 10:46:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 10:47:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 10:47:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 10:48:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 10:50:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 10:53:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 10:56:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 10:59:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 11:01:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Aug 06 11:22:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 00:16:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 00:21:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 00:23:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 00:24:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 00:26:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 00:27:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 00:28:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 00:28:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 00:31:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 00:33:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 00:36:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 00:39:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 00:41:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 01:01:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 19:30:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 19:36:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 19:37:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 19:38:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 19:39:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 19:39:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 08 19:40:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Aug 14 22:13:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Aug 14 22:17:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Aug 14 22:19:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Aug 14 22:21:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Aug 14 22:23:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Aug 14 22:23:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Aug 14 22:24:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Aug 14 22:24:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Aug 14 22:27:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Aug 14 22:30:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Aug 14 22:32:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Aug 14 22:35:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Aug 14 22:38:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Aug 14 22:58:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 15 00:43:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 15 00:49:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 15 00:50:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 15 00:51:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 15 00:51:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 15 00:52:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Aug 15 00:53:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 17 23:04:00 IST 2026</t>
-  </si>
-  <si>
     <t>Thu Sep 17 23:16:21 IST 2026</t>
   </si>
   <si>
@@ -1120,15 +241,6 @@
     <t>Thu Sep 17 23:28:37 IST 2026</t>
   </si>
   <si>
-    <t>Thu Sep 17 23:29:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 17 23:30:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 17 23:31:26 IST 2026</t>
-  </si>
-  <si>
     <t>Thu Sep 17 23:32:30 IST 2026</t>
   </si>
   <si>
@@ -1138,61 +250,37 @@
     <t>Thu Sep 17 23:37:54 IST 2026</t>
   </si>
   <si>
-    <t>Thu Sep 17 23:53:42 IST 2026</t>
-  </si>
-  <si>
     <t>Fri Sep 18 00:59:21 IST 2026</t>
   </si>
   <si>
-    <t>Fri Sep 18 01:03:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Sep 18 01:04:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Sep 18 01:05:22 IST 2026</t>
-  </si>
-  <si>
     <t>Fri Sep 18 01:06:05 IST 2026</t>
   </si>
   <si>
     <t>Fri Sep 18 01:06:54 IST 2026</t>
   </si>
   <si>
-    <t>Fri Sep 18 01:07:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Sep 22 20:01:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Sep 22 20:02:51 IST 2026</t>
-  </si>
-  <si>
     <t>Tue Sep 22 20:04:03 IST 2026</t>
   </si>
   <si>
-    <t>Tue Sep 22 20:18:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Sep 22 21:06:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Sep 22 21:13:08 IST 2026</t>
-  </si>
-  <si>
     <t>Tue Sep 22 21:15:57 IST 2026</t>
   </si>
   <si>
     <t>Tue Sep 22 23:27:32 IST 2026</t>
   </si>
   <si>
-    <t>Tue Sep 22 23:32:10 IST 2026</t>
-  </si>
-  <si>
     <t>Thu Sep 24 17:51:14 IST 2026</t>
   </si>
   <si>
     <t>Thu Sep 24 17:53:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:00:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:41:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 14:10:24 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1271,48 +359,48 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="2" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyBorder="1" applyNumberFormat="1" borderId="2" fillId="0" fontId="0" numFmtId="2" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="2" fillId="0" fontId="0" numFmtId="2" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1329,10 +417,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1367,7 +455,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1402,7 +490,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1496,21 +584,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1527,7 +615,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1579,18 +667,21 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.0"/>
+  </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1624,10 +715,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>370</v>
+        <v>64</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1655,7 +746,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>369</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -1678,10 +769,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>365</v>
+        <v>62</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -1703,7 +794,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1711,7 +802,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CFB1CD1-F3B6-43AC-8580-D3EB244DA395}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CFB1CD1-F3B6-43AC-8580-D3EB244DA395}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1721,7 +812,7 @@
     <col min="15" max="15" customWidth="true" width="12.36328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1753,27 +844,27 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row ht="130.5" r="2" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:15" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>342</v>
+        <v>49</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1796,28 +887,28 @@
         <v>6</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="M2" s="9">
         <v>28609</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A934BCA2-85F5-4C93-BBEE-2C380B06E8FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A934BCA2-85F5-4C93-BBEE-2C380B06E8FD}">
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1846,13 +937,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -1860,7 +951,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>360</v>
+        <v>60</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1877,10 +968,10 @@
         <v>Bridges</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -1888,10 +979,10 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>12</v>
@@ -1904,21 +995,21 @@
         <v>Bridges</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>52</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>12</v>
@@ -1931,27 +1022,27 @@
         <v>Bridges</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="G6" s="11" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="G7" s="11" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0B956F6-C214-41E0-9C06-CEBF82C79B1D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0B956F6-C214-41E0-9C06-CEBF82C79B1D}">
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1981,16 +1072,16 @@
         <v>5</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -1998,7 +1089,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>372</v>
+        <v>65</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -2015,24 +1106,24 @@
         <v>Bridges</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="J2" t="s" s="0">
-        <v>64</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>12</v>
@@ -2045,19 +1136,19 @@
         <v>Bridges</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>52</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14FA0791-CEBE-4D11-B2A1-F3F80E94D9F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14FA0791-CEBE-4D11-B2A1-F3F80E94D9F6}">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2085,16 +1176,16 @@
         <v>5</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -2102,7 +1193,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>358</v>
+        <v>67</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -2119,22 +1210,22 @@
         <v>Bridges</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="J2" t="s" s="0">
-        <v>63</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42D40E85-2D41-457A-88AE-C55FF8092C53}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42D40E85-2D41-457A-88AE-C55FF8092C53}">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -2158,16 +1249,16 @@
         <v>5</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -2175,7 +1266,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>361</v>
+        <v>61</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -2192,22 +1283,22 @@
         <v>Bridges</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="J2" t="s" s="0">
-        <v>63</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CCD7964-6EA7-47FC-8316-5BB19CD71397}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CCD7964-6EA7-47FC-8316-5BB19CD71397}">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -2231,16 +1322,16 @@
         <v>5</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -2248,7 +1339,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>373</v>
+        <v>66</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -2265,22 +1356,22 @@
         <v>Bridges</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="J2" t="s" s="0">
-        <v>63</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{971A235C-1EB8-4FB4-A052-AC25C4AD1D51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{971A235C-1EB8-4FB4-A052-AC25C4AD1D51}">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -2304,24 +1395,24 @@
         <v>5</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>12</v>
@@ -2334,26 +1425,26 @@
         <v>Bridges</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24D17964-3C9A-4128-9E79-065C6162AEA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24D17964-3C9A-4128-9E79-065C6162AEA0}">
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="12" max="12" customWidth="true" width="9.81640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2385,10 +1476,10 @@
         <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
@@ -2396,7 +1487,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>343</v>
+        <v>50</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2430,11 +1521,11 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3">
@@ -2456,11 +1547,11 @@
         <v>10</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3">
@@ -2478,19 +1569,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F3F653-DA45-4F17-B585-55D2A689218D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F3F653-DA45-4F17-B585-55D2A689218D}">
   <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="31.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2522,16 +1613,16 @@
         <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L1" s="4"/>
     </row>
-    <row ht="145" r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="145" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>345</v>
+        <v>52</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -2554,21 +1645,21 @@
         <v>6</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L2" s="5"/>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C63CEF1E-9472-4171-9CD3-FA3B036F7CBF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C63CEF1E-9472-4171-9CD3-FA3B036F7CBF}">
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2605,7 +1696,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>352</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2633,7 +1724,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>353</v>
+        <v>57</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -2659,7 +1750,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>354</v>
+        <v>58</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -2681,16 +1772,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{279D9BFE-7E90-4AE5-8638-D512C4CC008B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{279D9BFE-7E90-4AE5-8638-D512C4CC008B}">
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2727,7 +1818,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>346</v>
+        <v>53</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2755,7 +1846,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>347</v>
+        <v>54</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -2781,7 +1872,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>348</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -2803,16 +1894,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C743C20-9154-41EC-9178-39729EDF45F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C743C20-9154-41EC-9178-39729EDF45F3}">
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2846,10 +1937,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>371</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2873,16 +1964,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2AC4ABD-97C1-4B0A-A78A-1F57EE1A6D5C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2AC4ABD-97C1-4B0A-A78A-1F57EE1A6D5C}">
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2914,15 +2005,15 @@
         <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row ht="409.5" r="2" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>356</v>
+        <v>59</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -2945,20 +2036,20 @@
         <v>6</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62A0D7E3-B8FB-4BA8-A147-CA4665BD31FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62A0D7E3-B8FB-4BA8-A147-CA4665BD31FB}">
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2990,15 +2081,15 @@
         <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row ht="362.5" r="2" spans="1:11" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>344</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -3021,16 +2112,16 @@
         <v>6</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CB2C77F-A6BC-4072-8D66-A2FB7943F35E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CB2C77F-A6BC-4072-8D66-A2FB7943F35E}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3040,7 +2131,7 @@
     <col min="15" max="15" bestFit="true" customWidth="true" width="19.453125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3072,27 +2163,27 @@
         <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row ht="333.5" r="2" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:15" ht="333.5" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -3115,22 +2206,22 @@
         <v>6</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="M2" s="10">
         <v>28609</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>